--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A2DBDA-9730-4C9B-83F4-EEF8F2D4813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933DC650-9A9E-4457-B3EF-5607A6396A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="167">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>brezel</t>
+  </si>
+  <si>
+    <t>schawarma</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J151"/>
+  <dimension ref="B2:J152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2085,40 +2088,40 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="23" t="s">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="12">
+        <v>6</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B80" s="12">
-        <v>1</v>
-      </c>
-      <c r="C80" s="12">
-        <v>1</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.25">
@@ -2129,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.25">
@@ -2143,10 +2146,10 @@
         <v>1</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -2157,118 +2160,118 @@
         <v>1</v>
       </c>
       <c r="D83" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="12">
+        <v>1</v>
+      </c>
+      <c r="C84" s="12">
+        <v>1</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E84" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="5"/>
-      <c r="C87" s="7" t="s">
+    <row r="88" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="5"/>
+      <c r="C88" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D87" s="5"/>
-      <c r="E87" s="6"/>
-    </row>
-    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="25" t="s">
+      <c r="D88" s="5"/>
+      <c r="E88" s="6"/>
+    </row>
+    <row r="90" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="24"/>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D91" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E90" s="2" t="s">
+      <c r="E91" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B91" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="12">
-        <v>6</v>
-      </c>
-      <c r="D91" s="15" t="s">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="12">
+        <v>6</v>
+      </c>
+      <c r="D92" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E91" s="16" t="s">
+      <c r="E92" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="17">
-        <v>6</v>
-      </c>
-      <c r="D92" s="18" t="s">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="17">
+        <v>6</v>
+      </c>
+      <c r="D93" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E92" s="19" t="s">
+      <c r="E93" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="94" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="25" t="s">
+    <row r="95" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C94" s="24"/>
-      <c r="D94" s="24"/>
-      <c r="E94" s="24"/>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="24"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="24"/>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D95" s="9" t="s">
+      <c r="D96" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B96" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C96" s="12">
-        <v>6</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E96" s="16" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E97" s="21" t="s">
-        <v>104</v>
+      <c r="C97" s="12">
+        <v>6</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
@@ -2278,8 +2281,8 @@
       <c r="C98" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D98" s="15" t="s">
-        <v>106</v>
+      <c r="D98" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E98" s="21" t="s">
         <v>104</v>
@@ -2292,8 +2295,8 @@
       <c r="C99" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="22" t="s">
-        <v>107</v>
+      <c r="D99" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>104</v>
@@ -2306,8 +2309,8 @@
       <c r="C100" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="15" t="s">
-        <v>108</v>
+      <c r="D100" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2320,8 +2323,8 @@
       <c r="C101" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="18" t="s">
-        <v>105</v>
+      <c r="D101" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2334,8 +2337,8 @@
       <c r="C102" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="15" t="s">
-        <v>109</v>
+      <c r="D102" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2348,8 +2351,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="18" t="s">
-        <v>110</v>
+      <c r="D103" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2362,8 +2365,8 @@
       <c r="C104" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="15" t="s">
-        <v>111</v>
+      <c r="D104" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2376,8 +2379,8 @@
       <c r="C105" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="22" t="s">
-        <v>112</v>
+      <c r="D105" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2390,8 +2393,8 @@
       <c r="C106" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="15" t="s">
-        <v>113</v>
+      <c r="D106" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2404,8 +2407,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="22" t="s">
-        <v>114</v>
+      <c r="D107" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2418,8 +2421,8 @@
       <c r="C108" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="15" t="s">
-        <v>115</v>
+      <c r="D108" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2432,8 +2435,8 @@
       <c r="C109" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D109" s="18" t="s">
-        <v>116</v>
+      <c r="D109" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2446,8 +2449,8 @@
       <c r="C110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D110" s="15" t="s">
-        <v>117</v>
+      <c r="D110" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2460,8 +2463,8 @@
       <c r="C111" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D111" s="18" t="s">
-        <v>118</v>
+      <c r="D111" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2474,8 +2477,8 @@
       <c r="C112" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D112" s="15" t="s">
-        <v>119</v>
+      <c r="D112" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2488,8 +2491,8 @@
       <c r="C113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D113" s="18" t="s">
-        <v>120</v>
+      <c r="D113" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2502,8 +2505,8 @@
       <c r="C114" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="15" t="s">
-        <v>121</v>
+      <c r="D114" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2516,8 +2519,8 @@
       <c r="C115" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D115" s="18" t="s">
-        <v>122</v>
+      <c r="D115" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2530,8 +2533,8 @@
       <c r="C116" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D116" s="15" t="s">
-        <v>123</v>
+      <c r="D116" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2544,8 +2547,8 @@
       <c r="C117" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="18" t="s">
-        <v>124</v>
+      <c r="D117" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2558,8 +2561,8 @@
       <c r="C118" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="15" t="s">
-        <v>125</v>
+      <c r="D118" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
@@ -2572,8 +2575,8 @@
       <c r="C119" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D119" s="18" t="s">
-        <v>126</v>
+      <c r="D119" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="E119" s="21" t="s">
         <v>104</v>
@@ -2586,8 +2589,8 @@
       <c r="C120" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D120" s="15" t="s">
-        <v>127</v>
+      <c r="D120" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="E120" s="21" t="s">
         <v>104</v>
@@ -2600,47 +2603,47 @@
       <c r="C121" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D121" s="18" t="s">
-        <v>128</v>
+      <c r="D121" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="E121" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="123" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B123" s="25" t="s">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E122" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B124" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C123" s="24"/>
-      <c r="D123" s="24"/>
-      <c r="E123" s="24"/>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="24"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B125" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D124" s="9" t="s">
+      <c r="D125" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="12">
-        <v>2</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.25">
@@ -2650,8 +2653,8 @@
       <c r="C126" s="12">
         <v>2</v>
       </c>
-      <c r="D126" s="18" t="s">
-        <v>132</v>
+      <c r="D126" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="E126" s="16" t="s">
         <v>130</v>
@@ -2664,8 +2667,8 @@
       <c r="C127" s="12">
         <v>2</v>
       </c>
-      <c r="D127" s="15" t="s">
-        <v>133</v>
+      <c r="D127" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>130</v>
@@ -2678,8 +2681,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="22" t="s">
-        <v>134</v>
+      <c r="D128" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2692,8 +2695,8 @@
       <c r="C129" s="12">
         <v>2</v>
       </c>
-      <c r="D129" s="15" t="s">
-        <v>135</v>
+      <c r="D129" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2706,8 +2709,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="18" t="s">
-        <v>136</v>
+      <c r="D130" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2720,8 +2723,8 @@
       <c r="C131" s="12">
         <v>2</v>
       </c>
-      <c r="D131" s="15" t="s">
-        <v>137</v>
+      <c r="D131" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2734,8 +2737,8 @@
       <c r="C132" s="12">
         <v>2</v>
       </c>
-      <c r="D132" s="22" t="s">
-        <v>138</v>
+      <c r="D132" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2748,8 +2751,8 @@
       <c r="C133" s="12">
         <v>2</v>
       </c>
-      <c r="D133" s="15" t="s">
-        <v>139</v>
+      <c r="D133" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2762,8 +2765,8 @@
       <c r="C134" s="12">
         <v>2</v>
       </c>
-      <c r="D134" s="22" t="s">
-        <v>140</v>
+      <c r="D134" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2776,8 +2779,8 @@
       <c r="C135" s="12">
         <v>2</v>
       </c>
-      <c r="D135" s="15" t="s">
-        <v>141</v>
+      <c r="D135" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2790,8 +2793,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="22" t="s">
-        <v>142</v>
+      <c r="D136" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2804,8 +2807,8 @@
       <c r="C137" s="12">
         <v>2</v>
       </c>
-      <c r="D137" s="15" t="s">
-        <v>143</v>
+      <c r="D137" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2818,8 +2821,8 @@
       <c r="C138" s="12">
         <v>2</v>
       </c>
-      <c r="D138" s="18" t="s">
-        <v>144</v>
+      <c r="D138" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2832,8 +2835,8 @@
       <c r="C139" s="12">
         <v>2</v>
       </c>
-      <c r="D139" s="15" t="s">
-        <v>145</v>
+      <c r="D139" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2846,8 +2849,8 @@
       <c r="C140" s="12">
         <v>2</v>
       </c>
-      <c r="D140" s="18" t="s">
-        <v>146</v>
+      <c r="D140" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2860,8 +2863,8 @@
       <c r="C141" s="12">
         <v>2</v>
       </c>
-      <c r="D141" s="15" t="s">
-        <v>147</v>
+      <c r="D141" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2874,8 +2877,8 @@
       <c r="C142" s="12">
         <v>2</v>
       </c>
-      <c r="D142" s="18" t="s">
-        <v>148</v>
+      <c r="D142" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2888,8 +2891,8 @@
       <c r="C143" s="12">
         <v>2</v>
       </c>
-      <c r="D143" s="15" t="s">
-        <v>149</v>
+      <c r="D143" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2900,10 +2903,10 @@
         <v>5</v>
       </c>
       <c r="C144" s="12">
-        <v>6</v>
-      </c>
-      <c r="D144" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2914,10 +2917,10 @@
         <v>5</v>
       </c>
       <c r="C145" s="12">
-        <v>2</v>
-      </c>
-      <c r="D145" s="15" t="s">
-        <v>151</v>
+        <v>6</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2930,8 +2933,8 @@
       <c r="C146" s="12">
         <v>2</v>
       </c>
-      <c r="D146" s="18" t="s">
-        <v>152</v>
+      <c r="D146" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2942,10 +2945,10 @@
         <v>5</v>
       </c>
       <c r="C147" s="12">
-        <v>6</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>153</v>
+        <v>2</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2958,8 +2961,8 @@
       <c r="C148" s="12">
         <v>6</v>
       </c>
-      <c r="D148" s="18" t="s">
-        <v>154</v>
+      <c r="D148" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
@@ -2972,8 +2975,8 @@
       <c r="C149" s="12">
         <v>6</v>
       </c>
-      <c r="D149" s="15" t="s">
-        <v>155</v>
+      <c r="D149" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E149" s="16" t="s">
         <v>130</v>
@@ -2986,8 +2989,8 @@
       <c r="C150" s="12">
         <v>6</v>
       </c>
-      <c r="D150" s="22" t="s">
-        <v>156</v>
+      <c r="D150" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="E150" s="16" t="s">
         <v>130</v>
@@ -2998,12 +3001,26 @@
         <v>5</v>
       </c>
       <c r="C151" s="12">
+        <v>6</v>
+      </c>
+      <c r="D151" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E151" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B152" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="12">
         <v>2</v>
       </c>
-      <c r="D151" s="15" t="s">
+      <c r="D152" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E151" s="16" t="s">
+      <c r="E152" s="16" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3012,10 +3029,10 @@
     <sortCondition ref="D64:D73"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B124:E124"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B15:E15"/>

--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biamine\ressourcepack\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933DC650-9A9E-4457-B3EF-5607A6396A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A61182-EDEC-4D2E-9B6C-86B4086486CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Models" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="168">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>schawarma</t>
+  </si>
+  <si>
+    <t>trophy: BuildingContest 1</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J152"/>
+  <dimension ref="B2:J153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1297,13 +1300,13 @@
         <v>5</v>
       </c>
       <c r="C21" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -1318,10 +1321,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1336,10 +1339,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1351,13 +1354,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1372,10 +1375,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1390,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1408,10 +1411,10 @@
         <v>8</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1426,10 +1429,10 @@
         <v>8</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1444,10 +1447,10 @@
         <v>8</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1462,10 +1465,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1477,13 +1480,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -1495,13 +1498,13 @@
         <v>5</v>
       </c>
       <c r="C32" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -1516,50 +1519,54 @@
         <v>8</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="8"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="23" t="s">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="12">
+        <v>8</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="12">
-        <v>6</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
@@ -1570,10 +1577,10 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
@@ -1584,10 +1591,10 @@
         <v>6</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
@@ -1598,10 +1605,10 @@
         <v>6</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
@@ -1612,10 +1619,10 @@
         <v>6</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
@@ -1626,10 +1633,10 @@
         <v>6</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -1640,10 +1647,10 @@
         <v>6</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
@@ -1654,10 +1661,10 @@
         <v>6</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -1668,10 +1675,10 @@
         <v>6</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -1682,10 +1689,10 @@
         <v>6</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
@@ -1696,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
@@ -1710,10 +1717,10 @@
         <v>6</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -1724,10 +1731,10 @@
         <v>6</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -1738,10 +1745,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -1752,10 +1759,10 @@
         <v>6</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -1766,10 +1773,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -1780,10 +1787,10 @@
         <v>6</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -1794,10 +1801,10 @@
         <v>6</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -1808,10 +1815,10 @@
         <v>6</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
@@ -1822,10 +1829,10 @@
         <v>6</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
@@ -1836,10 +1843,10 @@
         <v>6</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -1850,10 +1857,10 @@
         <v>6</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
@@ -1864,10 +1871,10 @@
         <v>6</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
@@ -1878,46 +1885,46 @@
         <v>6</v>
       </c>
       <c r="D60" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="12">
+        <v>6</v>
+      </c>
+      <c r="D61" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E61" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="23" t="s">
+    <row r="63" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C64" s="12">
-        <v>6</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
@@ -1928,10 +1935,10 @@
         <v>6</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
@@ -1942,10 +1949,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
@@ -1956,10 +1963,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
@@ -1970,10 +1977,10 @@
         <v>6</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
@@ -1984,10 +1991,10 @@
         <v>6</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
@@ -1998,10 +2005,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -2012,10 +2019,10 @@
         <v>6</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
@@ -2026,10 +2033,10 @@
         <v>6</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
@@ -2040,10 +2047,10 @@
         <v>6</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
@@ -2054,10 +2061,10 @@
         <v>6</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
@@ -2068,10 +2075,10 @@
         <v>6</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
@@ -2082,10 +2089,10 @@
         <v>6</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.25">
@@ -2096,46 +2103,46 @@
         <v>6</v>
       </c>
       <c r="D77" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="12">
+        <v>6</v>
+      </c>
+      <c r="D78" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E78" s="14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="79" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="23" t="s">
+    <row r="80" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B81" s="12">
-        <v>1</v>
-      </c>
-      <c r="C81" s="12">
-        <v>1</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.25">
@@ -2146,10 +2153,10 @@
         <v>1</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -2160,10 +2167,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.25">
@@ -2174,118 +2181,118 @@
         <v>1</v>
       </c>
       <c r="D84" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" s="12">
+        <v>1</v>
+      </c>
+      <c r="C85" s="12">
+        <v>1</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E85" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="5"/>
-      <c r="C88" s="7" t="s">
+    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="5"/>
+      <c r="C89" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="6"/>
-    </row>
-    <row r="90" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="25" t="s">
+      <c r="D89" s="5"/>
+      <c r="E89" s="6"/>
+    </row>
+    <row r="91" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="24"/>
-      <c r="D90" s="24"/>
-      <c r="E90" s="24"/>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D91" s="9" t="s">
+      <c r="D92" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="12">
-        <v>6</v>
-      </c>
-      <c r="D92" s="15" t="s">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="12">
+        <v>6</v>
+      </c>
+      <c r="D93" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E92" s="16" t="s">
+      <c r="E93" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="17">
-        <v>6</v>
-      </c>
-      <c r="D93" s="18" t="s">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="17">
+        <v>6</v>
+      </c>
+      <c r="D94" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="E94" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="95" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="25" t="s">
+    <row r="96" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C95" s="24"/>
-      <c r="D95" s="24"/>
-      <c r="E95" s="24"/>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="24"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D97" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E97" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C97" s="12">
-        <v>6</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E97" s="16" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B98" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E98" s="21" t="s">
-        <v>104</v>
+      <c r="C98" s="12">
+        <v>6</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
@@ -2295,8 +2302,8 @@
       <c r="C99" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>106</v>
+      <c r="D99" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>104</v>
@@ -2309,8 +2316,8 @@
       <c r="C100" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="22" t="s">
-        <v>107</v>
+      <c r="D100" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2323,8 +2330,8 @@
       <c r="C101" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="15" t="s">
-        <v>108</v>
+      <c r="D101" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2337,8 +2344,8 @@
       <c r="C102" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="18" t="s">
-        <v>105</v>
+      <c r="D102" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2351,8 +2358,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="15" t="s">
-        <v>109</v>
+      <c r="D103" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2365,8 +2372,8 @@
       <c r="C104" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="18" t="s">
-        <v>110</v>
+      <c r="D104" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2379,8 +2386,8 @@
       <c r="C105" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="15" t="s">
-        <v>111</v>
+      <c r="D105" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2393,8 +2400,8 @@
       <c r="C106" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="22" t="s">
-        <v>112</v>
+      <c r="D106" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2407,8 +2414,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="15" t="s">
-        <v>113</v>
+      <c r="D107" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2421,8 +2428,8 @@
       <c r="C108" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="22" t="s">
-        <v>114</v>
+      <c r="D108" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2435,8 +2442,8 @@
       <c r="C109" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D109" s="15" t="s">
-        <v>115</v>
+      <c r="D109" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2449,8 +2456,8 @@
       <c r="C110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D110" s="18" t="s">
-        <v>116</v>
+      <c r="D110" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2463,8 +2470,8 @@
       <c r="C111" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D111" s="15" t="s">
-        <v>117</v>
+      <c r="D111" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2477,8 +2484,8 @@
       <c r="C112" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D112" s="18" t="s">
-        <v>118</v>
+      <c r="D112" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2491,8 +2498,8 @@
       <c r="C113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D113" s="15" t="s">
-        <v>119</v>
+      <c r="D113" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2505,8 +2512,8 @@
       <c r="C114" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="18" t="s">
-        <v>120</v>
+      <c r="D114" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2519,8 +2526,8 @@
       <c r="C115" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D115" s="15" t="s">
-        <v>121</v>
+      <c r="D115" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2533,8 +2540,8 @@
       <c r="C116" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D116" s="18" t="s">
-        <v>122</v>
+      <c r="D116" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2547,8 +2554,8 @@
       <c r="C117" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="15" t="s">
-        <v>123</v>
+      <c r="D117" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2561,8 +2568,8 @@
       <c r="C118" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="18" t="s">
-        <v>124</v>
+      <c r="D118" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
@@ -2575,8 +2582,8 @@
       <c r="C119" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D119" s="15" t="s">
-        <v>125</v>
+      <c r="D119" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E119" s="21" t="s">
         <v>104</v>
@@ -2589,8 +2596,8 @@
       <c r="C120" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D120" s="18" t="s">
-        <v>126</v>
+      <c r="D120" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="E120" s="21" t="s">
         <v>104</v>
@@ -2603,8 +2610,8 @@
       <c r="C121" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D121" s="15" t="s">
-        <v>127</v>
+      <c r="D121" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="E121" s="21" t="s">
         <v>104</v>
@@ -2617,47 +2624,47 @@
       <c r="C122" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D122" s="18" t="s">
-        <v>128</v>
+      <c r="D122" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="E122" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="124" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B124" s="25" t="s">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E123" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B125" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="24"/>
-      <c r="D124" s="24"/>
-      <c r="E124" s="24"/>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="1" t="s">
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B126" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D126" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E126" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B126" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C126" s="12">
-        <v>2</v>
-      </c>
-      <c r="D126" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E126" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.25">
@@ -2667,8 +2674,8 @@
       <c r="C127" s="12">
         <v>2</v>
       </c>
-      <c r="D127" s="18" t="s">
-        <v>132</v>
+      <c r="D127" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="E127" s="16" t="s">
         <v>130</v>
@@ -2681,8 +2688,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="15" t="s">
-        <v>133</v>
+      <c r="D128" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2695,8 +2702,8 @@
       <c r="C129" s="12">
         <v>2</v>
       </c>
-      <c r="D129" s="22" t="s">
-        <v>134</v>
+      <c r="D129" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2709,8 +2716,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="15" t="s">
-        <v>135</v>
+      <c r="D130" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2723,8 +2730,8 @@
       <c r="C131" s="12">
         <v>2</v>
       </c>
-      <c r="D131" s="18" t="s">
-        <v>136</v>
+      <c r="D131" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2737,8 +2744,8 @@
       <c r="C132" s="12">
         <v>2</v>
       </c>
-      <c r="D132" s="15" t="s">
-        <v>137</v>
+      <c r="D132" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2751,8 +2758,8 @@
       <c r="C133" s="12">
         <v>2</v>
       </c>
-      <c r="D133" s="22" t="s">
-        <v>138</v>
+      <c r="D133" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2765,8 +2772,8 @@
       <c r="C134" s="12">
         <v>2</v>
       </c>
-      <c r="D134" s="15" t="s">
-        <v>139</v>
+      <c r="D134" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2779,8 +2786,8 @@
       <c r="C135" s="12">
         <v>2</v>
       </c>
-      <c r="D135" s="22" t="s">
-        <v>140</v>
+      <c r="D135" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2793,8 +2800,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="15" t="s">
-        <v>141</v>
+      <c r="D136" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2807,8 +2814,8 @@
       <c r="C137" s="12">
         <v>2</v>
       </c>
-      <c r="D137" s="22" t="s">
-        <v>142</v>
+      <c r="D137" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2821,8 +2828,8 @@
       <c r="C138" s="12">
         <v>2</v>
       </c>
-      <c r="D138" s="15" t="s">
-        <v>143</v>
+      <c r="D138" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2835,8 +2842,8 @@
       <c r="C139" s="12">
         <v>2</v>
       </c>
-      <c r="D139" s="18" t="s">
-        <v>144</v>
+      <c r="D139" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2849,8 +2856,8 @@
       <c r="C140" s="12">
         <v>2</v>
       </c>
-      <c r="D140" s="15" t="s">
-        <v>145</v>
+      <c r="D140" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2863,8 +2870,8 @@
       <c r="C141" s="12">
         <v>2</v>
       </c>
-      <c r="D141" s="18" t="s">
-        <v>146</v>
+      <c r="D141" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2877,8 +2884,8 @@
       <c r="C142" s="12">
         <v>2</v>
       </c>
-      <c r="D142" s="15" t="s">
-        <v>147</v>
+      <c r="D142" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2891,8 +2898,8 @@
       <c r="C143" s="12">
         <v>2</v>
       </c>
-      <c r="D143" s="18" t="s">
-        <v>148</v>
+      <c r="D143" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2905,8 +2912,8 @@
       <c r="C144" s="12">
         <v>2</v>
       </c>
-      <c r="D144" s="15" t="s">
-        <v>149</v>
+      <c r="D144" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2917,10 +2924,10 @@
         <v>5</v>
       </c>
       <c r="C145" s="12">
-        <v>6</v>
-      </c>
-      <c r="D145" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2931,10 +2938,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="12">
-        <v>2</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>151</v>
+        <v>6</v>
+      </c>
+      <c r="D146" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2947,8 +2954,8 @@
       <c r="C147" s="12">
         <v>2</v>
       </c>
-      <c r="D147" s="18" t="s">
-        <v>152</v>
+      <c r="D147" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2959,10 +2966,10 @@
         <v>5</v>
       </c>
       <c r="C148" s="12">
-        <v>6</v>
-      </c>
-      <c r="D148" s="15" t="s">
-        <v>153</v>
+        <v>2</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
@@ -2975,8 +2982,8 @@
       <c r="C149" s="12">
         <v>6</v>
       </c>
-      <c r="D149" s="18" t="s">
-        <v>154</v>
+      <c r="D149" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E149" s="16" t="s">
         <v>130</v>
@@ -2989,8 +2996,8 @@
       <c r="C150" s="12">
         <v>6</v>
       </c>
-      <c r="D150" s="15" t="s">
-        <v>155</v>
+      <c r="D150" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E150" s="16" t="s">
         <v>130</v>
@@ -3003,8 +3010,8 @@
       <c r="C151" s="12">
         <v>6</v>
       </c>
-      <c r="D151" s="22" t="s">
-        <v>156</v>
+      <c r="D151" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="E151" s="16" t="s">
         <v>130</v>
@@ -3015,29 +3022,43 @@
         <v>5</v>
       </c>
       <c r="C152" s="12">
-        <v>2</v>
-      </c>
-      <c r="D152" s="15" t="s">
-        <v>157</v>
+        <v>6</v>
+      </c>
+      <c r="D152" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="E152" s="16" t="s">
         <v>130</v>
       </c>
     </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B153" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="12">
+        <v>2</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E153" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B64:E73">
-    <sortCondition ref="D64:D73"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B65:E74">
+    <sortCondition ref="D65:D74"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B125:E125"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biamine\ressourcepack\Ressourcepack-for-biamine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A61182-EDEC-4D2E-9B6C-86B4086486CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F72D77FB-B4F0-48F2-89EA-DD26ECB7F2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Models" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="170">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -524,6 +524,12 @@
   </si>
   <si>
     <t>trophy: BuildingContest 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - </t>
+  </si>
+  <si>
+    <t>trophy: Building contest 2</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J153"/>
+  <dimension ref="B2:J154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1315,16 +1321,16 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>5</v>
+        <v>168</v>
       </c>
       <c r="C22" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -1339,10 +1345,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1357,10 +1363,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1372,13 +1378,13 @@
         <v>5</v>
       </c>
       <c r="C25" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1393,10 +1399,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1411,10 +1417,10 @@
         <v>8</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1429,10 +1435,10 @@
         <v>8</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1447,10 +1453,10 @@
         <v>8</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1465,10 +1471,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1483,10 +1489,10 @@
         <v>8</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -1498,13 +1504,13 @@
         <v>5</v>
       </c>
       <c r="C32" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -1516,13 +1522,13 @@
         <v>5</v>
       </c>
       <c r="C33" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -1537,50 +1543,54 @@
         <v>8</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="8"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="23" t="s">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="12">
+        <v>8</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="12">
-        <v>6</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
@@ -1591,10 +1601,10 @@
         <v>6</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
@@ -1605,10 +1615,10 @@
         <v>6</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
@@ -1619,10 +1629,10 @@
         <v>6</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
@@ -1633,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -1647,10 +1657,10 @@
         <v>6</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
@@ -1661,10 +1671,10 @@
         <v>6</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -1675,10 +1685,10 @@
         <v>6</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
@@ -1689,10 +1699,10 @@
         <v>6</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
@@ -1703,10 +1713,10 @@
         <v>6</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
@@ -1717,10 +1727,10 @@
         <v>6</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -1731,10 +1741,10 @@
         <v>6</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
@@ -1745,10 +1755,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
@@ -1759,10 +1769,10 @@
         <v>6</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
@@ -1773,10 +1783,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
@@ -1787,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
@@ -1801,10 +1811,10 @@
         <v>6</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
@@ -1815,10 +1825,10 @@
         <v>6</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
@@ -1829,10 +1839,10 @@
         <v>6</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
@@ -1843,10 +1853,10 @@
         <v>6</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
@@ -1857,10 +1867,10 @@
         <v>6</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
@@ -1871,10 +1881,10 @@
         <v>6</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
@@ -1885,10 +1895,10 @@
         <v>6</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
@@ -1899,46 +1909,46 @@
         <v>6</v>
       </c>
       <c r="D61" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="12">
+        <v>6</v>
+      </c>
+      <c r="D62" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E62" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="63" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="23" t="s">
+    <row r="64" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="12">
-        <v>6</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
@@ -1949,10 +1959,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
@@ -1963,10 +1973,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.25">
@@ -1977,10 +1987,10 @@
         <v>6</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
@@ -1991,10 +2001,10 @@
         <v>6</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.25">
@@ -2005,10 +2015,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.25">
@@ -2019,10 +2029,10 @@
         <v>6</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.25">
@@ -2033,10 +2043,10 @@
         <v>6</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
@@ -2047,10 +2057,10 @@
         <v>6</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
@@ -2061,10 +2071,10 @@
         <v>6</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.25">
@@ -2075,10 +2085,10 @@
         <v>6</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.25">
@@ -2089,10 +2099,10 @@
         <v>6</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.25">
@@ -2103,10 +2113,10 @@
         <v>6</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.25">
@@ -2117,46 +2127,46 @@
         <v>6</v>
       </c>
       <c r="D78" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="12">
+        <v>6</v>
+      </c>
+      <c r="D79" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E79" s="14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B80" s="23" t="s">
+    <row r="81" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B82" s="12">
-        <v>1</v>
-      </c>
-      <c r="C82" s="12">
-        <v>1</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.25">
@@ -2167,10 +2177,10 @@
         <v>1</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.25">
@@ -2181,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.25">
@@ -2195,118 +2205,118 @@
         <v>1</v>
       </c>
       <c r="D85" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" s="12">
+        <v>1</v>
+      </c>
+      <c r="C86" s="12">
+        <v>1</v>
+      </c>
+      <c r="D86" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E86" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="5"/>
-      <c r="C89" s="7" t="s">
+    <row r="90" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="5"/>
+      <c r="C90" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="6"/>
-    </row>
-    <row r="91" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="25" t="s">
+      <c r="D90" s="5"/>
+      <c r="E90" s="6"/>
+    </row>
+    <row r="92" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="24"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D93" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E93" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="12">
-        <v>6</v>
-      </c>
-      <c r="D93" s="15" t="s">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="12">
+        <v>6</v>
+      </c>
+      <c r="D94" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E93" s="16" t="s">
+      <c r="E94" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="17">
-        <v>6</v>
-      </c>
-      <c r="D94" s="18" t="s">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="17">
+        <v>6</v>
+      </c>
+      <c r="D95" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E94" s="19" t="s">
+      <c r="E95" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="96" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="25" t="s">
+    <row r="97" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C96" s="24"/>
-      <c r="D96" s="24"/>
-      <c r="E96" s="24"/>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="1" t="s">
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D97" s="9" t="s">
+      <c r="D98" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="12">
-        <v>6</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C99" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E99" s="21" t="s">
-        <v>104</v>
+      <c r="C99" s="12">
+        <v>6</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
@@ -2316,8 +2326,8 @@
       <c r="C100" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="15" t="s">
-        <v>106</v>
+      <c r="D100" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>104</v>
@@ -2330,8 +2340,8 @@
       <c r="C101" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="22" t="s">
-        <v>107</v>
+      <c r="D101" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>104</v>
@@ -2344,8 +2354,8 @@
       <c r="C102" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="15" t="s">
-        <v>108</v>
+      <c r="D102" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>104</v>
@@ -2358,8 +2368,8 @@
       <c r="C103" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D103" s="18" t="s">
-        <v>105</v>
+      <c r="D103" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>104</v>
@@ -2372,8 +2382,8 @@
       <c r="C104" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D104" s="15" t="s">
-        <v>109</v>
+      <c r="D104" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>104</v>
@@ -2386,8 +2396,8 @@
       <c r="C105" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D105" s="18" t="s">
-        <v>110</v>
+      <c r="D105" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>104</v>
@@ -2400,8 +2410,8 @@
       <c r="C106" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D106" s="15" t="s">
-        <v>111</v>
+      <c r="D106" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>104</v>
@@ -2414,8 +2424,8 @@
       <c r="C107" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D107" s="22" t="s">
-        <v>112</v>
+      <c r="D107" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E107" s="21" t="s">
         <v>104</v>
@@ -2428,8 +2438,8 @@
       <c r="C108" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D108" s="15" t="s">
-        <v>113</v>
+      <c r="D108" s="22" t="s">
+        <v>112</v>
       </c>
       <c r="E108" s="21" t="s">
         <v>104</v>
@@ -2442,8 +2452,8 @@
       <c r="C109" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D109" s="22" t="s">
-        <v>114</v>
+      <c r="D109" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E109" s="21" t="s">
         <v>104</v>
@@ -2456,8 +2466,8 @@
       <c r="C110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D110" s="15" t="s">
-        <v>115</v>
+      <c r="D110" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>104</v>
@@ -2470,8 +2480,8 @@
       <c r="C111" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D111" s="18" t="s">
-        <v>116</v>
+      <c r="D111" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E111" s="21" t="s">
         <v>104</v>
@@ -2484,8 +2494,8 @@
       <c r="C112" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D112" s="15" t="s">
-        <v>117</v>
+      <c r="D112" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="E112" s="21" t="s">
         <v>104</v>
@@ -2498,8 +2508,8 @@
       <c r="C113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D113" s="18" t="s">
-        <v>118</v>
+      <c r="D113" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="E113" s="21" t="s">
         <v>104</v>
@@ -2512,8 +2522,8 @@
       <c r="C114" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="15" t="s">
-        <v>119</v>
+      <c r="D114" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="E114" s="21" t="s">
         <v>104</v>
@@ -2526,8 +2536,8 @@
       <c r="C115" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D115" s="18" t="s">
-        <v>120</v>
+      <c r="D115" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="E115" s="21" t="s">
         <v>104</v>
@@ -2540,8 +2550,8 @@
       <c r="C116" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D116" s="15" t="s">
-        <v>121</v>
+      <c r="D116" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E116" s="21" t="s">
         <v>104</v>
@@ -2554,8 +2564,8 @@
       <c r="C117" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D117" s="18" t="s">
-        <v>122</v>
+      <c r="D117" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="E117" s="21" t="s">
         <v>104</v>
@@ -2568,8 +2578,8 @@
       <c r="C118" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="15" t="s">
-        <v>123</v>
+      <c r="D118" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="E118" s="21" t="s">
         <v>104</v>
@@ -2582,8 +2592,8 @@
       <c r="C119" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D119" s="18" t="s">
-        <v>124</v>
+      <c r="D119" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="E119" s="21" t="s">
         <v>104</v>
@@ -2596,8 +2606,8 @@
       <c r="C120" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D120" s="15" t="s">
-        <v>125</v>
+      <c r="D120" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="E120" s="21" t="s">
         <v>104</v>
@@ -2610,8 +2620,8 @@
       <c r="C121" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D121" s="18" t="s">
-        <v>126</v>
+      <c r="D121" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="E121" s="21" t="s">
         <v>104</v>
@@ -2624,8 +2634,8 @@
       <c r="C122" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D122" s="15" t="s">
-        <v>127</v>
+      <c r="D122" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="E122" s="21" t="s">
         <v>104</v>
@@ -2638,47 +2648,47 @@
       <c r="C123" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D123" s="18" t="s">
-        <v>128</v>
+      <c r="D123" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="E123" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="125" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B125" s="25" t="s">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B126" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C125" s="24"/>
-      <c r="D125" s="24"/>
-      <c r="E125" s="24"/>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="24"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D126" s="9" t="s">
+      <c r="D127" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E127" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C127" s="12">
-        <v>2</v>
-      </c>
-      <c r="D127" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E127" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.25">
@@ -2688,8 +2698,8 @@
       <c r="C128" s="12">
         <v>2</v>
       </c>
-      <c r="D128" s="18" t="s">
-        <v>132</v>
+      <c r="D128" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="E128" s="16" t="s">
         <v>130</v>
@@ -2702,8 +2712,8 @@
       <c r="C129" s="12">
         <v>2</v>
       </c>
-      <c r="D129" s="15" t="s">
-        <v>133</v>
+      <c r="D129" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="E129" s="16" t="s">
         <v>130</v>
@@ -2716,8 +2726,8 @@
       <c r="C130" s="12">
         <v>2</v>
       </c>
-      <c r="D130" s="22" t="s">
-        <v>134</v>
+      <c r="D130" s="15" t="s">
+        <v>133</v>
       </c>
       <c r="E130" s="16" t="s">
         <v>130</v>
@@ -2730,8 +2740,8 @@
       <c r="C131" s="12">
         <v>2</v>
       </c>
-      <c r="D131" s="15" t="s">
-        <v>135</v>
+      <c r="D131" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="E131" s="16" t="s">
         <v>130</v>
@@ -2744,8 +2754,8 @@
       <c r="C132" s="12">
         <v>2</v>
       </c>
-      <c r="D132" s="18" t="s">
-        <v>136</v>
+      <c r="D132" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="E132" s="16" t="s">
         <v>130</v>
@@ -2758,8 +2768,8 @@
       <c r="C133" s="12">
         <v>2</v>
       </c>
-      <c r="D133" s="15" t="s">
-        <v>137</v>
+      <c r="D133" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="E133" s="16" t="s">
         <v>130</v>
@@ -2772,8 +2782,8 @@
       <c r="C134" s="12">
         <v>2</v>
       </c>
-      <c r="D134" s="22" t="s">
-        <v>138</v>
+      <c r="D134" s="15" t="s">
+        <v>137</v>
       </c>
       <c r="E134" s="16" t="s">
         <v>130</v>
@@ -2786,8 +2796,8 @@
       <c r="C135" s="12">
         <v>2</v>
       </c>
-      <c r="D135" s="15" t="s">
-        <v>139</v>
+      <c r="D135" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="E135" s="16" t="s">
         <v>130</v>
@@ -2800,8 +2810,8 @@
       <c r="C136" s="12">
         <v>2</v>
       </c>
-      <c r="D136" s="22" t="s">
-        <v>140</v>
+      <c r="D136" s="15" t="s">
+        <v>139</v>
       </c>
       <c r="E136" s="16" t="s">
         <v>130</v>
@@ -2814,8 +2824,8 @@
       <c r="C137" s="12">
         <v>2</v>
       </c>
-      <c r="D137" s="15" t="s">
-        <v>141</v>
+      <c r="D137" s="22" t="s">
+        <v>140</v>
       </c>
       <c r="E137" s="16" t="s">
         <v>130</v>
@@ -2828,8 +2838,8 @@
       <c r="C138" s="12">
         <v>2</v>
       </c>
-      <c r="D138" s="22" t="s">
-        <v>142</v>
+      <c r="D138" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="E138" s="16" t="s">
         <v>130</v>
@@ -2842,8 +2852,8 @@
       <c r="C139" s="12">
         <v>2</v>
       </c>
-      <c r="D139" s="15" t="s">
-        <v>143</v>
+      <c r="D139" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="E139" s="16" t="s">
         <v>130</v>
@@ -2856,8 +2866,8 @@
       <c r="C140" s="12">
         <v>2</v>
       </c>
-      <c r="D140" s="18" t="s">
-        <v>144</v>
+      <c r="D140" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E140" s="16" t="s">
         <v>130</v>
@@ -2870,8 +2880,8 @@
       <c r="C141" s="12">
         <v>2</v>
       </c>
-      <c r="D141" s="15" t="s">
-        <v>145</v>
+      <c r="D141" s="18" t="s">
+        <v>144</v>
       </c>
       <c r="E141" s="16" t="s">
         <v>130</v>
@@ -2884,8 +2894,8 @@
       <c r="C142" s="12">
         <v>2</v>
       </c>
-      <c r="D142" s="18" t="s">
-        <v>146</v>
+      <c r="D142" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="E142" s="16" t="s">
         <v>130</v>
@@ -2898,8 +2908,8 @@
       <c r="C143" s="12">
         <v>2</v>
       </c>
-      <c r="D143" s="15" t="s">
-        <v>147</v>
+      <c r="D143" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="E143" s="16" t="s">
         <v>130</v>
@@ -2912,8 +2922,8 @@
       <c r="C144" s="12">
         <v>2</v>
       </c>
-      <c r="D144" s="18" t="s">
-        <v>148</v>
+      <c r="D144" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="E144" s="16" t="s">
         <v>130</v>
@@ -2926,8 +2936,8 @@
       <c r="C145" s="12">
         <v>2</v>
       </c>
-      <c r="D145" s="15" t="s">
-        <v>149</v>
+      <c r="D145" s="18" t="s">
+        <v>148</v>
       </c>
       <c r="E145" s="16" t="s">
         <v>130</v>
@@ -2938,10 +2948,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="12">
-        <v>6</v>
-      </c>
-      <c r="D146" s="22" t="s">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E146" s="16" t="s">
         <v>130</v>
@@ -2952,10 +2962,10 @@
         <v>5</v>
       </c>
       <c r="C147" s="12">
-        <v>2</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>151</v>
+        <v>6</v>
+      </c>
+      <c r="D147" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="E147" s="16" t="s">
         <v>130</v>
@@ -2968,8 +2978,8 @@
       <c r="C148" s="12">
         <v>2</v>
       </c>
-      <c r="D148" s="18" t="s">
-        <v>152</v>
+      <c r="D148" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E148" s="16" t="s">
         <v>130</v>
@@ -2980,10 +2990,10 @@
         <v>5</v>
       </c>
       <c r="C149" s="12">
-        <v>6</v>
-      </c>
-      <c r="D149" s="15" t="s">
-        <v>153</v>
+        <v>2</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>152</v>
       </c>
       <c r="E149" s="16" t="s">
         <v>130</v>
@@ -2996,8 +3006,8 @@
       <c r="C150" s="12">
         <v>6</v>
       </c>
-      <c r="D150" s="18" t="s">
-        <v>154</v>
+      <c r="D150" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E150" s="16" t="s">
         <v>130</v>
@@ -3010,8 +3020,8 @@
       <c r="C151" s="12">
         <v>6</v>
       </c>
-      <c r="D151" s="15" t="s">
-        <v>155</v>
+      <c r="D151" s="18" t="s">
+        <v>154</v>
       </c>
       <c r="E151" s="16" t="s">
         <v>130</v>
@@ -3024,8 +3034,8 @@
       <c r="C152" s="12">
         <v>6</v>
       </c>
-      <c r="D152" s="22" t="s">
-        <v>156</v>
+      <c r="D152" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="E152" s="16" t="s">
         <v>130</v>
@@ -3036,29 +3046,43 @@
         <v>5</v>
       </c>
       <c r="C153" s="12">
-        <v>2</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>157</v>
+        <v>6</v>
+      </c>
+      <c r="D153" s="22" t="s">
+        <v>156</v>
       </c>
       <c r="E153" s="16" t="s">
         <v>130</v>
       </c>
     </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B154" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="12">
+        <v>2</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E154" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B65:E74">
-    <sortCondition ref="D65:D74"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B66:E75">
+    <sortCondition ref="D66:D75"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B126:E126"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cmdList.xlsx
+++ b/cmdList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bianca\Desktop\Server biamine\custom plugin\1_Resourcepacks\Github\Ressourcepack-for-biamine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F72D77FB-B4F0-48F2-89EA-DD26ECB7F2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A8C9F5-B45A-45C0-BF83-8D80E3E7E6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Models" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="171">
   <si>
     <t>Key (Legende)</t>
   </si>
@@ -530,6 +530,9 @@
   </si>
   <si>
     <t>trophy: Building contest 2</t>
+  </si>
+  <si>
+    <t>trophy halloween 2</t>
   </si>
 </sst>
 </file>
@@ -644,7 +647,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -668,6 +671,78 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -677,16 +752,25 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -712,9 +796,6 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -727,47 +808,1068 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4CAF7D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4CAF7D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4CAF7D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4CAF7D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFBFBFBF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFBFBFBF"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -784,6 +1886,97 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9572A079-6307-473F-BD3E-9E2388ABEEB5}" name="Tabelle1" displayName="Tabelle1" ref="B16:E36" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
+  <autoFilter ref="B16:E36" xr:uid="{9572A079-6307-473F-BD3E-9E2388ABEEB5}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0E540F8C-79C0-4F41-85E9-65558DCB6E08}" name="Use" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{FC624CEC-191E-4361-B738-14504F22E39B}" name="Kind of use" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{11B414CF-FD55-4970-B0DB-4695C175C1E7}" name="Kennzahl" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{6FF18EF8-EDF3-4110-9075-4C69A8326889}" name="For what" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{135FEC67-A7A2-4A21-BA46-B58CFC8008FE}" name="Tabelle2" displayName="Tabelle2" ref="B39:E63" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
+  <autoFilter ref="B39:E63" xr:uid="{135FEC67-A7A2-4A21-BA46-B58CFC8008FE}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D5F473C7-E827-42BB-B13B-A5A3AB5A946D}" name="Use" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{4A213B93-4628-4522-AF03-ED732EEA5AFD}" name="Kind of use" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{1A72504E-3C63-4C72-AA49-53160085BDFB}" name="Kennzahl" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{D14434BC-221E-4B3B-8859-3CC4F3665262}" name="For what" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{51768843-5D6A-464D-BF45-1A1DBDA42E0F}" name="Tabelle3" displayName="Tabelle3" ref="B66:E80" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="25" tableBorderDxfId="26" totalsRowBorderDxfId="24">
+  <autoFilter ref="B66:E80" xr:uid="{51768843-5D6A-464D-BF45-1A1DBDA42E0F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{2A4A7EEB-10E4-4B73-90ED-272BA3A7BB32}" name="Use" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{3BD2947C-C966-40C1-9431-036031040FBF}" name="Kind of use" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{F0C2003A-29FF-44ED-BCB4-23A9C74025B5}" name="Kennzahl" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{736C7AE0-E786-4381-9F10-1F061EFE20F7}" name="For what" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B76B63E3-89DB-421F-A37E-423CF0499352}" name="Tabelle4" displayName="Tabelle4" ref="B83:E87" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16">
+  <autoFilter ref="B83:E87" xr:uid="{B76B63E3-89DB-421F-A37E-423CF0499352}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{05408176-D9CD-48B9-BFBD-7F285A0839D8}" name="Use" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{E240072B-6A0D-46C0-89E3-8FDBA5ED9BFB}" name="Kind of use" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{A960301D-A4F2-41D3-AA89-C096DF8865A2}" name="Kennzahl" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{211557FE-009B-49AE-BA78-5A73BD343E42}" name="For what" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6898D942-2094-4BD9-9BC0-81AE054E35AC}" name="Tabelle5" displayName="Tabelle5" ref="B94:E96" totalsRowShown="0">
+  <autoFilter ref="B94:E96" xr:uid="{6898D942-2094-4BD9-9BC0-81AE054E35AC}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D03ACF19-51CB-44B4-BFA8-842AD90F3A1F}" name="Use" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D7F11764-D097-42A5-9C5F-172109C1A505}" name="Kind of use" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{962A8EB3-833E-44F7-973F-529F98054A15}" name="name"/>
+    <tableColumn id="4" xr3:uid="{C14312B8-E1C7-42F5-880E-775C13DEA8FA}" name="For what"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9045B76F-0103-48D6-BAE4-76AB4A329DE7}" name="Tabelle6" displayName="Tabelle6" ref="B99:E125" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="B99:E125" xr:uid="{9045B76F-0103-48D6-BAE4-76AB4A329DE7}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{9C525FE7-77B7-4F5A-989D-0B5FF0DDFFD2}" name="Use" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{866F687E-66EE-4D8B-B0F8-0417866177BF}" name="Kind of use" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{A8776F0D-F2B7-4257-8DA5-A17E6B2ACA16}" name="name" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{02AE87EE-A01B-42F6-B93F-820A409936E6}" name="For what" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{55B9E3EB-59F0-40F6-AA07-F86673D7C5AD}" name="Tabelle7" displayName="Tabelle7" ref="B128:E155" totalsRowShown="0">
+  <autoFilter ref="B128:E155" xr:uid="{55B9E3EB-59F0-40F6-AA07-F86673D7C5AD}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A5054DE8-5167-4889-874E-612EF10E3C9A}" name="Use" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{F530CE66-B578-4543-9974-141857BDB880}" name="Kind of use" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{E349115B-3C95-4072-8B9C-89857D7F258D}" name="name" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{61C4341B-4A3F-42F7-8CA5-9CC84901A836}" name="For what" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J154"/>
+  <dimension ref="B2:J155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1087,21 +2280,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -1118,86 +2311,86 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>1</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>2</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>1</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>3</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="10">
-        <v>6</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="B9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="9">
+        <v>6</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9">
         <v>7</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10">
+      <c r="B11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9">
         <v>8</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1216,66 +2409,66 @@
       <c r="E13" s="6"/>
     </row>
     <row r="15" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="12">
-        <v>6</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="B17" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="11">
+        <v>6</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="12">
-        <v>6</v>
-      </c>
-      <c r="D18" s="13" t="s">
+      <c r="B18" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="11">
+        <v>6</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="18" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="12">
-        <v>6</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="B19" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="11">
+        <v>6</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="18" t="s">
         <v>37</v>
       </c>
       <c r="G19" s="3"/>
@@ -1284,16 +2477,16 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="12">
-        <v>6</v>
-      </c>
-      <c r="D20" s="13" t="s">
+      <c r="B20" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="11">
+        <v>6</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="18" t="s">
         <v>162</v>
       </c>
       <c r="G20" s="3"/>
@@ -1302,16 +2495,16 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="12">
-        <v>6</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="B21" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="11">
+        <v>6</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="18" t="s">
         <v>167</v>
       </c>
       <c r="G21" s="3"/>
@@ -1320,16 +2513,16 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="12">
-        <v>6</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="11">
+        <v>6</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="18" t="s">
         <v>169</v>
       </c>
       <c r="G22" s="3"/>
@@ -1338,17 +2531,17 @@
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="12">
-        <v>7</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>30</v>
+      <c r="B23" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="11">
+        <v>6</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>170</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1356,17 +2549,17 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="12">
+      <c r="B24" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="11">
         <v>7</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>31</v>
+      <c r="D24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -1374,17 +2567,17 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="12">
+      <c r="B25" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="11">
         <v>7</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>32</v>
+      <c r="D25" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -1392,17 +2585,17 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="12">
-        <v>8</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>17</v>
+      <c r="B26" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="11">
+        <v>7</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1410,17 +2603,17 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="12">
+      <c r="B27" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="11">
         <v>8</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>19</v>
+      <c r="D27" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -1428,17 +2621,17 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="12">
+      <c r="B28" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="11">
         <v>8</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>21</v>
+      <c r="D28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -1446,17 +2639,17 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="12">
+      <c r="B29" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="11">
         <v>8</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>23</v>
+      <c r="D29" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>21</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -1464,17 +2657,17 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="12">
+      <c r="B30" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="11">
         <v>8</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>25</v>
+      <c r="D30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -1482,17 +2675,17 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="12">
+      <c r="B31" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="11">
         <v>8</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>27</v>
+      <c r="D31" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>25</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -1500,17 +2693,17 @@
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="12">
+      <c r="B32" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="11">
         <v>8</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>29</v>
+      <c r="D32" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -1518,17 +2711,17 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="12">
-        <v>6</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>39</v>
+      <c r="B33" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="11">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>29</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -1536,17 +2729,17 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="12">
-        <v>8</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>41</v>
+      <c r="B34" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="11">
+        <v>6</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>39</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -1554,1537 +2747,1564 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="12">
+      <c r="B35" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="11">
         <v>8</v>
       </c>
-      <c r="D35" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>43</v>
+      <c r="D35" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>41</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="8"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="23" t="s">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="23">
+        <v>8</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="12">
-        <v>6</v>
-      </c>
-      <c r="D39" s="13" t="s">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="11">
+        <v>6</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E40" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="12">
-        <v>6</v>
-      </c>
-      <c r="D40" s="13" t="s">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="11">
+        <v>6</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E41" s="18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="12">
-        <v>6</v>
-      </c>
-      <c r="D41" s="13" t="s">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="11">
+        <v>6</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E42" s="18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="12">
-        <v>6</v>
-      </c>
-      <c r="D42" s="13" t="s">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="11">
+        <v>6</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E43" s="18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="12">
-        <v>6</v>
-      </c>
-      <c r="D43" s="13" t="s">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="11">
+        <v>6</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E44" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="12">
-        <v>6</v>
-      </c>
-      <c r="D44" s="13" t="s">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="11">
+        <v>6</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E45" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="12">
-        <v>6</v>
-      </c>
-      <c r="D45" s="13" t="s">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="11">
+        <v>6</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E46" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="12">
-        <v>6</v>
-      </c>
-      <c r="D46" s="13" t="s">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="11">
+        <v>6</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E47" s="18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="12">
-        <v>6</v>
-      </c>
-      <c r="D47" s="13" t="s">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="11">
+        <v>6</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E48" s="18" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="12">
-        <v>6</v>
-      </c>
-      <c r="D48" s="13" t="s">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="11">
+        <v>6</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E49" s="18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="12">
-        <v>6</v>
-      </c>
-      <c r="D49" s="13" t="s">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="11">
+        <v>6</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E50" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="12">
-        <v>6</v>
-      </c>
-      <c r="D50" s="13" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="11">
+        <v>6</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E51" s="18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="12">
-        <v>6</v>
-      </c>
-      <c r="D51" s="13" t="s">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="11">
+        <v>6</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E52" s="18" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="12">
-        <v>6</v>
-      </c>
-      <c r="D52" s="13" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="11">
+        <v>6</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E53" s="18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="12">
-        <v>6</v>
-      </c>
-      <c r="D53" s="13" t="s">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="11">
+        <v>6</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E54" s="18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="12">
-        <v>6</v>
-      </c>
-      <c r="D54" s="13" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="11">
+        <v>6</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E55" s="18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="12">
-        <v>6</v>
-      </c>
-      <c r="D55" s="13" t="s">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="11">
+        <v>6</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E56" s="18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="12">
-        <v>6</v>
-      </c>
-      <c r="D56" s="13" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="11">
+        <v>6</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E57" s="18" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="12">
-        <v>6</v>
-      </c>
-      <c r="D57" s="13" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="11">
+        <v>6</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E58" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="12">
-        <v>6</v>
-      </c>
-      <c r="D58" s="13" t="s">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="11">
+        <v>6</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E59" s="18" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="12">
-        <v>6</v>
-      </c>
-      <c r="D59" s="13" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="11">
+        <v>6</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E60" s="18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="12">
-        <v>6</v>
-      </c>
-      <c r="D60" s="13" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="11">
+        <v>6</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E61" s="18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" s="12">
-        <v>6</v>
-      </c>
-      <c r="D61" s="13" t="s">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="11">
+        <v>6</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E62" s="18" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="12">
-        <v>6</v>
-      </c>
-      <c r="D62" s="13" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="23">
+        <v>6</v>
+      </c>
+      <c r="D63" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E63" s="25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="23" t="s">
+    <row r="65" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C66" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D66" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E66" s="21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="12">
-        <v>6</v>
-      </c>
-      <c r="D66" s="13" t="s">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="11">
+        <v>6</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E67" s="18" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="12">
-        <v>6</v>
-      </c>
-      <c r="D67" s="13" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="11">
+        <v>6</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E68" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="12">
-        <v>6</v>
-      </c>
-      <c r="D68" s="13" t="s">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="11">
+        <v>6</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E69" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="12">
-        <v>6</v>
-      </c>
-      <c r="D69" s="13" t="s">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="11">
+        <v>6</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E70" s="18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="12">
-        <v>6</v>
-      </c>
-      <c r="D70" s="13" t="s">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B71" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="11">
+        <v>6</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E71" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B71" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="12">
-        <v>6</v>
-      </c>
-      <c r="D71" s="13" t="s">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="11">
+        <v>6</v>
+      </c>
+      <c r="D72" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E72" s="18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="12">
-        <v>6</v>
-      </c>
-      <c r="D72" s="13" t="s">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="11">
+        <v>6</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E73" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="12">
-        <v>6</v>
-      </c>
-      <c r="D73" s="13" t="s">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="11">
+        <v>6</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E74" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="12">
-        <v>6</v>
-      </c>
-      <c r="D74" s="13" t="s">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="11">
+        <v>6</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E75" s="18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="12">
-        <v>6</v>
-      </c>
-      <c r="D75" s="13" t="s">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="11">
+        <v>6</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E76" s="18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="12">
-        <v>6</v>
-      </c>
-      <c r="D76" s="13" t="s">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="11">
+        <v>6</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E77" s="18" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B77" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="12">
-        <v>6</v>
-      </c>
-      <c r="D77" s="13" t="s">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="11">
+        <v>6</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E78" s="18" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B78" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="12">
-        <v>6</v>
-      </c>
-      <c r="D78" s="13" t="s">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="11">
+        <v>6</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E79" s="18" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B79" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="12">
-        <v>6</v>
-      </c>
-      <c r="D79" s="13" t="s">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B80" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="23">
+        <v>6</v>
+      </c>
+      <c r="D80" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E80" s="25" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="23" t="s">
+    <row r="82" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C83" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E83" s="21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B83" s="12">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="17">
         <v>1</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C84" s="11">
         <v>1</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D84" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E84" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B84" s="12">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" s="17">
         <v>1</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C85" s="11">
         <v>1</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D85" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E85" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B85" s="12">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" s="17">
         <v>1</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C86" s="11">
         <v>1</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D86" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E86" s="18" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B86" s="12">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" s="22">
         <v>1</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C87" s="23">
         <v>1</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D87" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E87" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="5"/>
-      <c r="C90" s="7" t="s">
+    <row r="91" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="5"/>
+      <c r="C91" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="6"/>
-    </row>
-    <row r="92" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="25" t="s">
+      <c r="D91" s="5"/>
+      <c r="E91" s="6"/>
+    </row>
+    <row r="93" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D94" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E94" s="30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="12">
-        <v>6</v>
-      </c>
-      <c r="D94" s="15" t="s">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="31">
+        <v>6</v>
+      </c>
+      <c r="D95" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E94" s="16" t="s">
+      <c r="E95" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B95" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="17">
-        <v>6</v>
-      </c>
-      <c r="D95" s="18" t="s">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="31">
+        <v>6</v>
+      </c>
+      <c r="D96" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E96" s="36" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="97" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="25" t="s">
+    <row r="98" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
-      <c r="E97" s="24"/>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D98" s="9" t="s">
+      <c r="D99" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E99" s="30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B99" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" s="12">
-        <v>6</v>
-      </c>
-      <c r="D99" s="15" t="s">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="31">
+        <v>6</v>
+      </c>
+      <c r="D100" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E99" s="16" t="s">
+      <c r="E100" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B100" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="18" t="s">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="E100" s="21" t="s">
+      <c r="E101" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B101" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" s="15" t="s">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="E101" s="21" t="s">
+      <c r="E102" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B102" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C102" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="22" t="s">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="E102" s="21" t="s">
+      <c r="E103" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B103" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D103" s="15" t="s">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="E103" s="21" t="s">
+      <c r="E104" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B104" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C104" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D104" s="18" t="s">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B105" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="E104" s="21" t="s">
+      <c r="E105" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B105" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C105" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D105" s="15" t="s">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B106" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E105" s="21" t="s">
+      <c r="E106" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B106" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D106" s="18" t="s">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B107" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="E106" s="21" t="s">
+      <c r="E107" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B107" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C107" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D107" s="15" t="s">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B108" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="E107" s="21" t="s">
+      <c r="E108" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C108" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D108" s="22" t="s">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B109" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="E108" s="21" t="s">
+      <c r="E109" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B109" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C109" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109" s="15" t="s">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B110" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E109" s="21" t="s">
+      <c r="E110" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B110" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C110" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D110" s="22" t="s">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B111" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="E110" s="21" t="s">
+      <c r="E111" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B111" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C111" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D111" s="15" t="s">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B112" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E111" s="21" t="s">
+      <c r="E112" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B112" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="18" t="s">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="E112" s="21" t="s">
+      <c r="E113" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B113" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C113" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D113" s="15" t="s">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B114" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E113" s="21" t="s">
+      <c r="E114" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B114" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D114" s="18" t="s">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B115" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="E114" s="21" t="s">
+      <c r="E115" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B115" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D115" s="15" t="s">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B116" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="E115" s="21" t="s">
+      <c r="E116" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B116" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C116" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D116" s="18" t="s">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B117" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="E116" s="21" t="s">
+      <c r="E117" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B117" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D117" s="15" t="s">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B118" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E117" s="21" t="s">
+      <c r="E118" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B118" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D118" s="18" t="s">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="E118" s="21" t="s">
+      <c r="E119" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B119" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C119" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D119" s="15" t="s">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="E119" s="21" t="s">
+      <c r="E120" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B120" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C120" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="18" t="s">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="E120" s="21" t="s">
+      <c r="E121" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B121" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" s="15" t="s">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E121" s="21" t="s">
+      <c r="E122" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D122" s="18" t="s">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E122" s="21" t="s">
+      <c r="E123" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D123" s="15" t="s">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="E123" s="21" t="s">
+      <c r="E124" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D124" s="18" t="s">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B125" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="E124" s="21" t="s">
+      <c r="E125" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="126" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B126" s="25" t="s">
+    <row r="127" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B127" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C126" s="24"/>
-      <c r="D126" s="24"/>
-      <c r="E126" s="24"/>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="27"/>
+      <c r="D127" s="27"/>
+      <c r="E127" s="27"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C128" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D128" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E128" s="30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B128" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C128" s="12">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="31">
         <v>2</v>
       </c>
-      <c r="D128" s="15" t="s">
+      <c r="D129" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="E128" s="16" t="s">
+      <c r="E129" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C129" s="12">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="31">
         <v>2</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="D130" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="E129" s="16" t="s">
+      <c r="E130" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C130" s="12">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="31">
         <v>2</v>
       </c>
-      <c r="D130" s="15" t="s">
+      <c r="D131" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="E130" s="16" t="s">
+      <c r="E131" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C131" s="12">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="31">
         <v>2</v>
       </c>
-      <c r="D131" s="22" t="s">
+      <c r="D132" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="E131" s="16" t="s">
+      <c r="E132" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C132" s="12">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="31">
         <v>2</v>
       </c>
-      <c r="D132" s="15" t="s">
+      <c r="D133" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="E132" s="16" t="s">
+      <c r="E133" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B133" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="12">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="31">
         <v>2</v>
       </c>
-      <c r="D133" s="18" t="s">
+      <c r="D134" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="E133" s="16" t="s">
+      <c r="E134" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B134" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C134" s="12">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B135" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="31">
         <v>2</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D135" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="E134" s="16" t="s">
+      <c r="E135" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B135" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="12">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B136" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="31">
         <v>2</v>
       </c>
-      <c r="D135" s="22" t="s">
+      <c r="D136" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="E135" s="16" t="s">
+      <c r="E136" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B136" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C136" s="12">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B137" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="31">
         <v>2</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="D137" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="E136" s="16" t="s">
+      <c r="E137" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B137" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C137" s="12">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B138" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="31">
         <v>2</v>
       </c>
-      <c r="D137" s="22" t="s">
+      <c r="D138" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="E137" s="16" t="s">
+      <c r="E138" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B138" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C138" s="12">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B139" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C139" s="31">
         <v>2</v>
       </c>
-      <c r="D138" s="15" t="s">
+      <c r="D139" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="E138" s="16" t="s">
+      <c r="E139" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B139" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C139" s="12">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B140" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="31">
         <v>2</v>
       </c>
-      <c r="D139" s="22" t="s">
+      <c r="D140" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="E139" s="16" t="s">
+      <c r="E140" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C140" s="12">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B141" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="31">
         <v>2</v>
       </c>
-      <c r="D140" s="15" t="s">
+      <c r="D141" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="E140" s="16" t="s">
+      <c r="E141" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B141" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C141" s="12">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B142" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="31">
         <v>2</v>
       </c>
-      <c r="D141" s="18" t="s">
+      <c r="D142" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="E141" s="16" t="s">
+      <c r="E142" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B142" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C142" s="12">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B143" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="31">
         <v>2</v>
       </c>
-      <c r="D142" s="15" t="s">
+      <c r="D143" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="E142" s="16" t="s">
+      <c r="E143" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B143" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C143" s="12">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B144" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="31">
         <v>2</v>
       </c>
-      <c r="D143" s="18" t="s">
+      <c r="D144" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="E143" s="16" t="s">
+      <c r="E144" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B144" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C144" s="12">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B145" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="31">
         <v>2</v>
       </c>
-      <c r="D144" s="15" t="s">
+      <c r="D145" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E145" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B145" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C145" s="12">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="31">
         <v>2</v>
       </c>
-      <c r="D145" s="18" t="s">
+      <c r="D146" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="E145" s="16" t="s">
+      <c r="E146" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C146" s="12">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="31">
         <v>2</v>
       </c>
-      <c r="D146" s="15" t="s">
+      <c r="D147" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E146" s="16" t="s">
+      <c r="E147" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B147" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C147" s="12">
-        <v>6</v>
-      </c>
-      <c r="D147" s="22" t="s">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="31">
+        <v>6</v>
+      </c>
+      <c r="D148" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="E147" s="16" t="s">
+      <c r="E148" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C148" s="12">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="31">
         <v>2</v>
       </c>
-      <c r="D148" s="15" t="s">
+      <c r="D149" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="E148" s="16" t="s">
+      <c r="E149" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B149" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C149" s="12">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="31">
         <v>2</v>
       </c>
-      <c r="D149" s="18" t="s">
+      <c r="D150" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="E149" s="16" t="s">
+      <c r="E150" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C150" s="12">
-        <v>6</v>
-      </c>
-      <c r="D150" s="15" t="s">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="31">
+        <v>6</v>
+      </c>
+      <c r="D151" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="E150" s="16" t="s">
+      <c r="E151" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B151" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C151" s="12">
-        <v>6</v>
-      </c>
-      <c r="D151" s="18" t="s">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B152" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="31">
+        <v>6</v>
+      </c>
+      <c r="D152" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="E151" s="16" t="s">
+      <c r="E152" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B152" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C152" s="12">
-        <v>6</v>
-      </c>
-      <c r="D152" s="15" t="s">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B153" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="31">
+        <v>6</v>
+      </c>
+      <c r="D153" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="E152" s="16" t="s">
+      <c r="E153" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B153" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C153" s="12">
-        <v>6</v>
-      </c>
-      <c r="D153" s="22" t="s">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B154" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="31">
+        <v>6</v>
+      </c>
+      <c r="D154" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="E153" s="16" t="s">
+      <c r="E154" s="33" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B154" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C154" s="12">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B155" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="31">
         <v>2</v>
       </c>
-      <c r="D154" s="15" t="s">
+      <c r="D155" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="E154" s="16" t="s">
+      <c r="E155" s="33" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B66:E75">
-    <sortCondition ref="D66:D75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B67:E76">
+    <sortCondition ref="D67:D76"/>
   </sortState>
   <mergeCells count="9">
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B127:E127"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="7">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+  </tableParts>
 </worksheet>
 </file>